--- a/diseases/d031/1995-1999.xlsx
+++ b/diseases/d031/1995-1999.xlsx
@@ -773,6 +773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4625,6 +4750,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4997,6 +5127,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5369,6 +5504,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5741,6 +5881,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6113,6 +6258,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6485,6 +6635,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6857,6 +7012,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7229,6 +7389,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7601,6 +7766,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7973,6 +8143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8343,6 +8518,11 @@
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">

--- a/diseases/d031/1995-1999.xlsx
+++ b/diseases/d031/1995-1999.xlsx
@@ -768,11 +768,6 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3918,11 +3603,6 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3615,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4068,11 +3738,6 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,22 +3750,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4218,11 +3873,6 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,22 +3885,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4368,11 +4008,6 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,22 +4020,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4466,17 +4091,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4501,172 +4126,80 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="O27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN27" t="b">
-        <v>0</v>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4728,28 +4261,23 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4762,22 +4290,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4843,17 +4361,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4878,172 +4396,80 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN29" t="b">
-        <v>0</v>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5105,28 +4531,23 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5139,22 +4560,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5220,17 +4631,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5255,172 +4666,80 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
-        <v>0</v>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5482,28 +4801,23 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5516,22 +4830,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5597,17 +4901,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5632,172 +4936,80 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N33" t="n">
         <v>12</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+      <c r="O33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>0</v>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5859,28 +5071,23 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5893,22 +5100,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5974,17 +5171,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6009,172 +5206,80 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>63</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>0</v>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6236,28 +5341,23 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6270,22 +5370,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6351,17 +5441,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6386,2434 +5476,80 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-12-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>46</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="O37" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN37" t="b">
-        <v>0</v>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1999-07-01</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>1999-07</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>9</v>
-      </c>
-      <c r="O38" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV38" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA38" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB38" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC38" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1999-07-01</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1999-07</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>20</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV39" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA39" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC39" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1999-08-01</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1999-08</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>12</v>
-      </c>
-      <c r="O40" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV40" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA40" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB40" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC40" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1999-08-01</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>1999-08</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>14</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV41" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA41" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB41" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC41" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1999-09-01</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>1999-09</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV42" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA42" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC42" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1999-09-01</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>1999-09</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>29</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP43" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV43" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA43" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC43" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1999-10-01</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>1999-10</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>7</v>
-      </c>
-      <c r="O44" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV44" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA44" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC44" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>1999-10-01</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1999-10</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>45</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV45" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA45" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC45" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>1999-11-01</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1999-11</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV46" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1999-11-01</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1999-11</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>52</v>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP47" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV47" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA47" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB47" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC47" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>11</v>
-      </c>
-      <c r="O48" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV48" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA48" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB48" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC48" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>scarlet-fever</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>D031</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Scarlet fever</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>猩红热</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>103</v>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Skarlatsótt</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA49" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC49" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8943,7 +5679,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -8963,7 +5699,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8973,7 +5709,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d031/1995-1999.xlsx
+++ b/diseases/d031/1995-1999.xlsx
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4126,80 +4126,172 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
-      </c>
-      <c r="O27" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>0</v>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4261,19 +4353,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4361,17 +4453,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4396,80 +4488,172 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>0</v>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4531,19 +4715,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -4631,17 +4815,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4666,80 +4850,172 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>22</v>
-      </c>
-      <c r="O31" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>0</v>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4801,19 +5077,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -4901,17 +5177,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4936,80 +5212,172 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N33" t="n">
         <v>12</v>
       </c>
-      <c r="O33" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>0</v>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5071,19 +5439,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5171,17 +5539,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5206,80 +5574,172 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>0</v>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5341,19 +5801,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -5441,17 +5901,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5476,80 +5936,2344 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
-      </c>
-      <c r="O37" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>0</v>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1999-07-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1999-07</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="AW37" t="inlineStr">
+      <c r="AW38" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="BA37" t="inlineStr">
+      <c r="BA38" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr">
+      <c r="BB38" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1999-07-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1999-07</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>20</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>12</v>
+      </c>
+      <c r="O40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>14</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>29</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>45</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>7</v>
+      </c>
+      <c r="O46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>52</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>11</v>
+      </c>
+      <c r="O48" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>scarlet-fever</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>103</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_A38_SKARLATSOTT_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Skarlatsótt</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 A38; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5679,7 +8403,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -5699,7 +8423,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -5709,7 +8433,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d031/1995-1999.xlsx
+++ b/diseases/d031/1995-1999.xlsx
@@ -768,6 +768,11 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,13 +785,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -903,6 +918,11 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,13 +935,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1038,6 +1068,11 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,13 +1085,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1173,6 +1218,11 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,13 +1235,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1308,6 +1368,11 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,13 +1385,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1443,6 +1518,11 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,13 +1535,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1578,6 +1668,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,13 +1685,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1713,6 +1818,11 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,13 +1835,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1848,6 +1968,11 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,13 +1985,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1983,6 +2118,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,13 +2135,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2118,6 +2268,11 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,13 +2285,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2253,6 +2418,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,13 +2435,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2388,6 +2568,11 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,13 +2585,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2523,6 +2718,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,13 +2735,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2658,6 +2868,11 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,13 +2885,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2793,6 +3018,11 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,13 +3035,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2928,6 +3168,11 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,13 +3185,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3063,6 +3318,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,13 +3335,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3198,6 +3468,11 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,13 +3485,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3333,6 +3618,11 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,13 +3635,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3468,6 +3768,11 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,13 +3785,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3603,6 +3918,11 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,13 +3935,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3738,6 +4068,11 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,13 +4085,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3873,6 +4218,11 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,13 +4235,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4008,6 +4368,11 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,13 +4385,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4370,6 +4745,11 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4382,13 +4762,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4732,6 +5122,11 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4744,13 +5139,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5094,6 +5499,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5106,13 +5516,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5456,6 +5876,11 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5468,13 +5893,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5818,6 +6253,11 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5830,13 +6270,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6180,6 +6630,11 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6192,13 +6647,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6542,6 +7007,11 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6554,13 +7024,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6904,6 +7384,11 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6916,13 +7401,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7266,6 +7761,11 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7278,13 +7778,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7628,6 +8138,11 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7640,13 +8155,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7990,6 +8515,11 @@
       <c r="Q48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8002,12 +8532,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
